--- a/Result/profitability/2461.xlsx
+++ b/Result/profitability/2461.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.4</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01499999999999996</v>
+        <v>0.02999999999999997</v>
       </c>
       <c r="N2" t="n">
-        <v>23.3225</v>
+        <v>23.7475</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.49</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04874999999999996</v>
+        <v>0.115</v>
       </c>
       <c r="N3" t="n">
-        <v>23.88625</v>
+        <v>24.6475</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.6</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1475</v>
+        <v>0.17375</v>
       </c>
       <c r="N4" t="n">
-        <v>23.67875</v>
+        <v>24.135</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02999999999999996</v>
+        <v>0.14125</v>
       </c>
       <c r="N5" t="n">
-        <v>23.18125</v>
+        <v>24.14875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.19</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1225</v>
+        <v>0.1524999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>23.74375</v>
+        <v>24.66875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.04</v>
       </c>
       <c r="M7" t="n">
-        <v>0.115</v>
+        <v>0.19375</v>
       </c>
       <c r="N7" t="n">
-        <v>24.31125</v>
+        <v>25.37625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.36</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1962499999999999</v>
+        <v>0.2012499999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>25.32125</v>
+        <v>25.43375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1899,7 +1899,7 @@
         <v>0.13</v>
       </c>
       <c r="M12" t="n">
-        <v>0.05999999999999996</v>
+        <v>0.05999999999999994</v>
       </c>
       <c r="N12" t="n">
         <v>24.50875</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2461</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1305</v>
+      </c>
+      <c r="D75" t="n">
+        <v>946</v>
+      </c>
+      <c r="E75" t="n">
+        <v>359</v>
+      </c>
+      <c r="F75" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="G75" t="n">
+        <v>98</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>7.53%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J75" t="n">
+        <v>82</v>
+      </c>
+      <c r="K75" t="n">
+        <v>63</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.007499999999999965</v>
+      </c>
+      <c r="N75" t="n">
+        <v>22.7975</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.04000000000000004</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1333333333333335</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.9000000000000021</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.03382187147688853</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.8900000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.618181818181818</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>7.740000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.3915022761760243</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
